--- a/Design-Files/MVP-Dash-v1.0/BOM/eSpark_BOM.xlsx
+++ b/Design-Files/MVP-Dash-v1.0/BOM/eSpark_BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="945">
   <si>
     <t>Component list</t>
   </si>
@@ -2830,6 +2830,30 @@
   </si>
   <si>
     <t>Order From Client Side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mating Connector </t>
+  </si>
+  <si>
+    <t>3 35P 4mm - Automobile Connectors ROHS</t>
+  </si>
+  <si>
+    <t>K776280H-35-PTW</t>
+  </si>
+  <si>
+    <t>Mating pin Terminal</t>
+  </si>
+  <si>
+    <t>Automobile Connectors ROHS</t>
+  </si>
+  <si>
+    <t>K776280T-PSN</t>
+  </si>
+  <si>
+    <t>C5138066</t>
+  </si>
+  <si>
+    <t>C2997465</t>
   </si>
 </sst>
 </file>
@@ -3728,7 +3752,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S199"/>
+  <dimension ref="A1:S201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="10" bestFit="1" customWidth="1"/>
@@ -13863,10 +13887,10 @@
       <c r="R184" s="14"/>
       <c r="S184" s="52"/>
     </row>
-    <row r="185" spans="1:19" s="53" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A185" s="51"/>
       <c r="B185" s="16">
-        <f t="shared" ref="B185" si="171">ROW(B185) - ROW($B$7)</f>
+        <f t="shared" ref="B185:B187" si="171">ROW(B185) - ROW($B$7)</f>
         <v>178</v>
       </c>
       <c r="C185" s="23" t="s">
@@ -13906,72 +13930,187 @@
       <c r="N185" s="14"/>
       <c r="O185" s="45"/>
       <c r="P185" s="15"/>
-      <c r="Q185" s="15"/>
+      <c r="Q185" s="15">
+        <f t="shared" ref="Q185:Q187" si="172">P185*N185</f>
+        <v>0</v>
+      </c>
       <c r="R185" s="14"/>
       <c r="S185" s="54" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="186" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="1"/>
-      <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
-      <c r="E186" s="1"/>
-      <c r="F186" s="1"/>
-      <c r="G186" s="1"/>
-      <c r="H186" s="1"/>
-      <c r="I186" s="1"/>
-      <c r="J186" s="1"/>
-      <c r="K186" s="1"/>
-      <c r="L186" s="1"/>
-      <c r="M186" s="1"/>
-      <c r="N186" s="57" t="s">
+    <row r="186" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A186" s="51"/>
+      <c r="B186" s="16">
+        <f t="shared" si="171"/>
+        <v>179</v>
+      </c>
+      <c r="C186" s="23" t="s">
+        <v>930</v>
+      </c>
+      <c r="D186" s="14" t="s">
+        <v>937</v>
+      </c>
+      <c r="E186" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="F186" s="14" t="s">
+        <v>933</v>
+      </c>
+      <c r="G186" s="14" t="s">
+        <v>939</v>
+      </c>
+      <c r="H186" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="I186" s="14" t="s">
+        <v>919</v>
+      </c>
+      <c r="J186" s="14" t="s">
+        <v>943</v>
+      </c>
+      <c r="K186" s="14" t="s">
+        <v>919</v>
+      </c>
+      <c r="L186" s="14">
+        <v>1</v>
+      </c>
+      <c r="M186" s="14">
+        <f>L186*5</f>
+        <v>5</v>
+      </c>
+      <c r="N186" s="14">
+        <v>6</v>
+      </c>
+      <c r="O186" s="45" t="s">
+        <v>921</v>
+      </c>
+      <c r="P186" s="15">
+        <v>4.5503</v>
+      </c>
+      <c r="Q186" s="15">
+        <f t="shared" si="172"/>
+        <v>27.3018</v>
+      </c>
+      <c r="R186" s="14"/>
+      <c r="S186" s="54"/>
+    </row>
+    <row r="187" spans="1:19" s="53" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="51"/>
+      <c r="B187" s="16">
+        <f t="shared" si="171"/>
+        <v>180</v>
+      </c>
+      <c r="C187" s="23" t="s">
+        <v>930</v>
+      </c>
+      <c r="D187" s="14" t="s">
+        <v>940</v>
+      </c>
+      <c r="E187" s="14" t="s">
+        <v>941</v>
+      </c>
+      <c r="F187" s="14" t="s">
+        <v>933</v>
+      </c>
+      <c r="G187" s="14" t="s">
+        <v>942</v>
+      </c>
+      <c r="H187" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="I187" s="14" t="s">
+        <v>919</v>
+      </c>
+      <c r="J187" s="14" t="s">
+        <v>944</v>
+      </c>
+      <c r="K187" s="14" t="s">
+        <v>919</v>
+      </c>
+      <c r="L187" s="14">
+        <v>35</v>
+      </c>
+      <c r="M187" s="14">
+        <f>L187*5</f>
+        <v>175</v>
+      </c>
+      <c r="N187" s="14">
+        <v>180</v>
+      </c>
+      <c r="O187" s="45" t="s">
+        <v>921</v>
+      </c>
+      <c r="P187" s="15">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="Q187" s="15">
+        <f t="shared" si="172"/>
+        <v>7.5060000000000002</v>
+      </c>
+      <c r="R187" s="14"/>
+      <c r="S187" s="54"/>
+    </row>
+    <row r="188" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+      <c r="L188" s="1"/>
+      <c r="M188" s="1"/>
+      <c r="N188" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="O186" s="58"/>
-      <c r="P186" s="58"/>
-      <c r="Q186" s="18">
-        <f>SUM(Q8:Q185)</f>
-        <v>607.79399999999998</v>
-      </c>
-      <c r="R186" s="1"/>
-      <c r="S186" s="1"/>
-    </row>
-    <row r="187" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="1"/>
-      <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
-      <c r="E187" s="1"/>
-      <c r="F187" s="1"/>
-      <c r="G187" s="1"/>
-      <c r="H187" s="1"/>
-      <c r="I187" s="1"/>
-      <c r="J187" s="1"/>
-      <c r="K187" s="1"/>
-      <c r="L187" s="1"/>
-      <c r="M187" s="1"/>
-      <c r="N187" s="57" t="s">
+      <c r="O188" s="58"/>
+      <c r="P188" s="58"/>
+      <c r="Q188" s="18">
+        <f>SUM(Q8:Q187)</f>
+        <v>642.60179999999991</v>
+      </c>
+      <c r="R188" s="1"/>
+      <c r="S188" s="1"/>
+    </row>
+    <row r="189" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="1"/>
+      <c r="G189" s="1"/>
+      <c r="H189" s="1"/>
+      <c r="I189" s="1"/>
+      <c r="J189" s="1"/>
+      <c r="K189" s="1"/>
+      <c r="L189" s="1"/>
+      <c r="M189" s="1"/>
+      <c r="N189" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="O187" s="58"/>
-      <c r="P187" s="58"/>
-      <c r="Q187" s="19">
-        <f>Q186/5</f>
-        <v>121.55879999999999</v>
-      </c>
-      <c r="R187" s="1"/>
-      <c r="S187" s="1"/>
-    </row>
-    <row r="199" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M199" s="38"/>
+      <c r="O189" s="58"/>
+      <c r="P189" s="58"/>
+      <c r="Q189" s="19">
+        <f>Q188/5</f>
+        <v>128.52035999999998</v>
+      </c>
+      <c r="R189" s="1"/>
+      <c r="S189" s="1"/>
+    </row>
+    <row r="201" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M201" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="K1:S1"/>
-    <mergeCell ref="N186:P186"/>
-    <mergeCell ref="N187:P187"/>
+    <mergeCell ref="N188:P188"/>
+    <mergeCell ref="N189:P189"/>
     <mergeCell ref="S2:S6"/>
   </mergeCells>
   <hyperlinks>
@@ -14147,9 +14286,11 @@
     <hyperlink ref="O172" r:id="rId170"/>
     <hyperlink ref="O113" r:id="rId171"/>
     <hyperlink ref="O148" r:id="rId172"/>
+    <hyperlink ref="O186" r:id="rId173"/>
+    <hyperlink ref="O187" r:id="rId174"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId173"/>
-  <drawing r:id="rId174"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId175"/>
+  <drawing r:id="rId176"/>
 </worksheet>
 </file>
--- a/Design-Files/MVP-Dash-v1.0/BOM/eSpark_BOM.xlsx
+++ b/Design-Files/MVP-Dash-v1.0/BOM/eSpark_BOM.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\alastair-baronessalpha\Design-Files\MVP-Dash-v1.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\eSpark-Consultants\alastair-baronessalpha\Design-Files\MVP-Dash-v1.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11C29E6-91E3-4787-8D63-0FC4C17867C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="946">
   <si>
     <t>Component list</t>
   </si>
@@ -2835,37 +2847,40 @@
     <t xml:space="preserve">Mating Connector </t>
   </si>
   <si>
-    <t>3 35P 4mm - Automobile Connectors ROHS</t>
-  </si>
-  <si>
-    <t>K776280H-35-PTW</t>
-  </si>
-  <si>
     <t>Mating pin Terminal</t>
   </si>
   <si>
-    <t>Automobile Connectors ROHS</t>
-  </si>
-  <si>
-    <t>K776280T-PSN</t>
-  </si>
-  <si>
-    <t>C5138066</t>
-  </si>
-  <si>
-    <t>C2997465</t>
+    <t>Rectangular Connector Housings Receptacle</t>
+  </si>
+  <si>
+    <t>Rectangular Connector Pin</t>
+  </si>
+  <si>
+    <t>90311-026LF</t>
+  </si>
+  <si>
+    <t>77138-101LF</t>
+  </si>
+  <si>
+    <t>Amphenol ICC</t>
+  </si>
+  <si>
+    <t>C5413172</t>
+  </si>
+  <si>
+    <t>C254717</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3041,6 +3056,12 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3243,7 +3264,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3310,15 +3331,15 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3327,19 +3348,19 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3409,6 +3430,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3750,10 +3774,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S201"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="10" bestFit="1" customWidth="1"/>
@@ -3775,7 +3799,7 @@
     <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="15.75" thickBot="1">
       <c r="A1" s="1"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3796,7 +3820,7 @@
       <c r="R1" s="55"/>
       <c r="S1" s="56"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
       <c r="B2" s="7"/>
       <c r="C2" s="13"/>
@@ -3821,7 +3845,7 @@
       <c r="R2" s="32"/>
       <c r="S2" s="59"/>
     </row>
-    <row r="3" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="16.5" thickBot="1">
       <c r="A3" s="1"/>
       <c r="B3" s="8"/>
       <c r="C3" s="26"/>
@@ -3846,7 +3870,7 @@
       <c r="R3" s="24"/>
       <c r="S3" s="60"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19">
       <c r="A4" s="1"/>
       <c r="B4" s="8"/>
       <c r="C4" s="26"/>
@@ -3867,7 +3891,7 @@
       <c r="R4" s="24"/>
       <c r="S4" s="60"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19">
       <c r="A5" s="1"/>
       <c r="B5" s="9"/>
       <c r="C5" s="33"/>
@@ -3888,7 +3912,7 @@
       <c r="R5" s="35"/>
       <c r="S5" s="60"/>
     </row>
-    <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="36"/>
@@ -3909,7 +3933,7 @@
       <c r="R6" s="35"/>
       <c r="S6" s="61"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="15.75" thickBot="1">
       <c r="A7" s="1"/>
       <c r="B7" s="12" t="s">
         <v>2</v>
@@ -3966,7 +3990,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" s="53" customFormat="1">
       <c r="A8" s="51"/>
       <c r="B8" s="16">
         <f>ROW(B8) - ROW($B$7)</f>
@@ -4022,7 +4046,7 @@
       <c r="R8" s="14"/>
       <c r="S8" s="52"/>
     </row>
-    <row r="9" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A9" s="51"/>
       <c r="B9" s="17">
         <f t="shared" ref="B9:B183" si="0">ROW(B9) - ROW($B$7)</f>
@@ -4078,7 +4102,7 @@
       <c r="R9" s="20"/>
       <c r="S9" s="20"/>
     </row>
-    <row r="10" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A10" s="51"/>
       <c r="B10" s="16">
         <f>ROW(B10) - ROW($B$7)</f>
@@ -4134,7 +4158,7 @@
       <c r="R10" s="14"/>
       <c r="S10" s="52"/>
     </row>
-    <row r="11" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" s="53" customFormat="1">
       <c r="A11" s="51"/>
       <c r="B11" s="17">
         <f t="shared" si="0"/>
@@ -4190,7 +4214,7 @@
       <c r="R11" s="20"/>
       <c r="S11" s="20"/>
     </row>
-    <row r="12" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A12" s="51"/>
       <c r="B12" s="16">
         <f>ROW(B12) - ROW($B$7)</f>
@@ -4246,7 +4270,7 @@
       <c r="R12" s="14"/>
       <c r="S12" s="52"/>
     </row>
-    <row r="13" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" s="53" customFormat="1">
       <c r="A13" s="51"/>
       <c r="B13" s="17">
         <f t="shared" si="0"/>
@@ -4302,7 +4326,7 @@
       <c r="R13" s="20"/>
       <c r="S13" s="20"/>
     </row>
-    <row r="14" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A14" s="51"/>
       <c r="B14" s="16">
         <f>ROW(B14) - ROW($B$7)</f>
@@ -4358,7 +4382,7 @@
       <c r="R14" s="14"/>
       <c r="S14" s="52"/>
     </row>
-    <row r="15" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" s="53" customFormat="1">
       <c r="A15" s="51"/>
       <c r="B15" s="17">
         <f t="shared" si="0"/>
@@ -4414,7 +4438,7 @@
       <c r="R15" s="20"/>
       <c r="S15" s="20"/>
     </row>
-    <row r="16" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" s="53" customFormat="1">
       <c r="A16" s="51"/>
       <c r="B16" s="16">
         <f>ROW(B16) - ROW($B$7)</f>
@@ -4470,7 +4494,7 @@
       <c r="R16" s="14"/>
       <c r="S16" s="52"/>
     </row>
-    <row r="17" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" s="53" customFormat="1">
       <c r="A17" s="51"/>
       <c r="B17" s="17">
         <f t="shared" si="0"/>
@@ -4526,7 +4550,7 @@
       <c r="R17" s="20"/>
       <c r="S17" s="20"/>
     </row>
-    <row r="18" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" s="53" customFormat="1">
       <c r="A18" s="51"/>
       <c r="B18" s="16">
         <f>ROW(B18) - ROW($B$7)</f>
@@ -4582,7 +4606,7 @@
       <c r="R18" s="14"/>
       <c r="S18" s="52"/>
     </row>
-    <row r="19" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" s="53" customFormat="1">
       <c r="A19" s="51"/>
       <c r="B19" s="17">
         <f t="shared" si="0"/>
@@ -4638,7 +4662,7 @@
       <c r="R19" s="20"/>
       <c r="S19" s="20"/>
     </row>
-    <row r="20" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A20" s="51"/>
       <c r="B20" s="16">
         <f>ROW(B20) - ROW($B$7)</f>
@@ -4694,7 +4718,7 @@
       <c r="R20" s="14"/>
       <c r="S20" s="52"/>
     </row>
-    <row r="21" spans="1:19" s="53" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" s="53" customFormat="1" ht="120">
       <c r="A21" s="51"/>
       <c r="B21" s="17">
         <f t="shared" si="0"/>
@@ -4750,7 +4774,7 @@
       <c r="R21" s="20"/>
       <c r="S21" s="20"/>
     </row>
-    <row r="22" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A22" s="51"/>
       <c r="B22" s="16">
         <f>ROW(B22) - ROW($B$7)</f>
@@ -4806,7 +4830,7 @@
       <c r="R22" s="14"/>
       <c r="S22" s="52"/>
     </row>
-    <row r="23" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" s="53" customFormat="1">
       <c r="A23" s="51"/>
       <c r="B23" s="17">
         <f t="shared" si="0"/>
@@ -4862,7 +4886,7 @@
       <c r="R23" s="20"/>
       <c r="S23" s="20"/>
     </row>
-    <row r="24" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" s="53" customFormat="1">
       <c r="A24" s="51"/>
       <c r="B24" s="16">
         <f>ROW(B24) - ROW($B$7)</f>
@@ -4918,7 +4942,7 @@
       <c r="R24" s="14"/>
       <c r="S24" s="52"/>
     </row>
-    <row r="25" spans="1:19" s="53" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" s="53" customFormat="1" ht="72">
       <c r="A25" s="51"/>
       <c r="B25" s="17">
         <f t="shared" si="0"/>
@@ -4974,7 +4998,7 @@
       <c r="R25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" s="53" customFormat="1">
       <c r="A26" s="51"/>
       <c r="B26" s="16">
         <f>ROW(B26) - ROW($B$7)</f>
@@ -5030,7 +5054,7 @@
       <c r="R26" s="14"/>
       <c r="S26" s="52"/>
     </row>
-    <row r="27" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A27" s="51"/>
       <c r="B27" s="17">
         <f t="shared" si="0"/>
@@ -5086,7 +5110,7 @@
       <c r="R27" s="20"/>
       <c r="S27" s="20"/>
     </row>
-    <row r="28" spans="1:19" s="53" customFormat="1" ht="96" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" s="53" customFormat="1" ht="96">
       <c r="A28" s="51"/>
       <c r="B28" s="16">
         <f>ROW(B28) - ROW($B$7)</f>
@@ -5142,7 +5166,7 @@
       <c r="R28" s="14"/>
       <c r="S28" s="52"/>
     </row>
-    <row r="29" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" s="53" customFormat="1">
       <c r="A29" s="51"/>
       <c r="B29" s="17">
         <f t="shared" si="0"/>
@@ -5198,7 +5222,7 @@
       <c r="R29" s="20"/>
       <c r="S29" s="20"/>
     </row>
-    <row r="30" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A30" s="51"/>
       <c r="B30" s="16">
         <f>ROW(B30) - ROW($B$7)</f>
@@ -5254,7 +5278,7 @@
       <c r="R30" s="14"/>
       <c r="S30" s="52"/>
     </row>
-    <row r="31" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" s="53" customFormat="1">
       <c r="A31" s="51"/>
       <c r="B31" s="17">
         <f t="shared" si="0"/>
@@ -5310,7 +5334,7 @@
       <c r="R31" s="20"/>
       <c r="S31" s="20"/>
     </row>
-    <row r="32" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A32" s="51"/>
       <c r="B32" s="16">
         <f>ROW(B32) - ROW($B$7)</f>
@@ -5366,7 +5390,7 @@
       <c r="R32" s="14"/>
       <c r="S32" s="52"/>
     </row>
-    <row r="33" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" s="53" customFormat="1">
       <c r="A33" s="51"/>
       <c r="B33" s="17">
         <f t="shared" si="0"/>
@@ -5423,7 +5447,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="34" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" s="53" customFormat="1">
       <c r="A34" s="51"/>
       <c r="B34" s="16">
         <f>ROW(B34) - ROW($B$7)</f>
@@ -5479,7 +5503,7 @@
       <c r="R34" s="14"/>
       <c r="S34" s="52"/>
     </row>
-    <row r="35" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" s="53" customFormat="1">
       <c r="A35" s="51"/>
       <c r="B35" s="17">
         <f t="shared" si="0"/>
@@ -5535,7 +5559,7 @@
       <c r="R35" s="20"/>
       <c r="S35" s="20"/>
     </row>
-    <row r="36" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="53" customFormat="1">
       <c r="A36" s="51"/>
       <c r="B36" s="16">
         <f>ROW(B36) - ROW($B$7)</f>
@@ -5591,7 +5615,7 @@
       <c r="R36" s="14"/>
       <c r="S36" s="52"/>
     </row>
-    <row r="37" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" s="53" customFormat="1">
       <c r="A37" s="51"/>
       <c r="B37" s="17">
         <f t="shared" si="0"/>
@@ -5647,7 +5671,7 @@
       <c r="R37" s="20"/>
       <c r="S37" s="20"/>
     </row>
-    <row r="38" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" s="53" customFormat="1">
       <c r="A38" s="51"/>
       <c r="B38" s="16">
         <f>ROW(B38) - ROW($B$7)</f>
@@ -5703,7 +5727,7 @@
       <c r="R38" s="14"/>
       <c r="S38" s="52"/>
     </row>
-    <row r="39" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" s="53" customFormat="1">
       <c r="A39" s="51"/>
       <c r="B39" s="17">
         <f t="shared" si="0"/>
@@ -5759,7 +5783,7 @@
       <c r="R39" s="20"/>
       <c r="S39" s="20"/>
     </row>
-    <row r="40" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" s="53" customFormat="1">
       <c r="A40" s="51"/>
       <c r="B40" s="16">
         <f>ROW(B40) - ROW($B$7)</f>
@@ -5815,7 +5839,7 @@
       <c r="R40" s="14"/>
       <c r="S40" s="52"/>
     </row>
-    <row r="41" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A41" s="51"/>
       <c r="B41" s="17">
         <f t="shared" si="0"/>
@@ -5871,7 +5895,7 @@
       <c r="R41" s="20"/>
       <c r="S41" s="20"/>
     </row>
-    <row r="42" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" s="53" customFormat="1">
       <c r="A42" s="51"/>
       <c r="B42" s="16">
         <f>ROW(B42) - ROW($B$7)</f>
@@ -5927,7 +5951,7 @@
       <c r="R42" s="14"/>
       <c r="S42" s="52"/>
     </row>
-    <row r="43" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" s="53" customFormat="1">
       <c r="A43" s="51"/>
       <c r="B43" s="17">
         <f t="shared" si="0"/>
@@ -5983,7 +6007,7 @@
       <c r="R43" s="20"/>
       <c r="S43" s="20"/>
     </row>
-    <row r="44" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" s="53" customFormat="1">
       <c r="A44" s="51"/>
       <c r="B44" s="16">
         <f>ROW(B44) - ROW($B$7)</f>
@@ -6039,7 +6063,7 @@
       <c r="R44" s="14"/>
       <c r="S44" s="52"/>
     </row>
-    <row r="45" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" s="53" customFormat="1">
       <c r="A45" s="51"/>
       <c r="B45" s="17">
         <f t="shared" si="0"/>
@@ -6095,7 +6119,7 @@
       <c r="R45" s="20"/>
       <c r="S45" s="20"/>
     </row>
-    <row r="46" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" s="53" customFormat="1">
       <c r="A46" s="51"/>
       <c r="B46" s="16">
         <f>ROW(B46) - ROW($B$7)</f>
@@ -6151,7 +6175,7 @@
       <c r="R46" s="14"/>
       <c r="S46" s="52"/>
     </row>
-    <row r="47" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" s="53" customFormat="1">
       <c r="A47" s="51"/>
       <c r="B47" s="17">
         <f t="shared" si="0"/>
@@ -6207,7 +6231,7 @@
       <c r="R47" s="20"/>
       <c r="S47" s="20"/>
     </row>
-    <row r="48" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" s="53" customFormat="1">
       <c r="A48" s="51"/>
       <c r="B48" s="16">
         <f>ROW(B48) - ROW($B$7)</f>
@@ -6263,7 +6287,7 @@
       <c r="R48" s="14"/>
       <c r="S48" s="52"/>
     </row>
-    <row r="49" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A49" s="51"/>
       <c r="B49" s="17">
         <f t="shared" si="0"/>
@@ -6319,7 +6343,7 @@
       <c r="R49" s="20"/>
       <c r="S49" s="20"/>
     </row>
-    <row r="50" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A50" s="51"/>
       <c r="B50" s="16">
         <f>ROW(B50) - ROW($B$7)</f>
@@ -6375,7 +6399,7 @@
       <c r="R50" s="14"/>
       <c r="S50" s="52"/>
     </row>
-    <row r="51" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A51" s="51"/>
       <c r="B51" s="17">
         <f t="shared" si="0"/>
@@ -6431,7 +6455,7 @@
       <c r="R51" s="20"/>
       <c r="S51" s="20"/>
     </row>
-    <row r="52" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" s="53" customFormat="1">
       <c r="A52" s="51"/>
       <c r="B52" s="16">
         <f>ROW(B52) - ROW($B$7)</f>
@@ -6487,7 +6511,7 @@
       <c r="R52" s="14"/>
       <c r="S52" s="52"/>
     </row>
-    <row r="53" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A53" s="51"/>
       <c r="B53" s="17">
         <f t="shared" si="0"/>
@@ -6543,7 +6567,7 @@
       <c r="R53" s="20"/>
       <c r="S53" s="20"/>
     </row>
-    <row r="54" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" s="53" customFormat="1">
       <c r="A54" s="51"/>
       <c r="B54" s="16">
         <f>ROW(B54) - ROW($B$7)</f>
@@ -6599,7 +6623,7 @@
       <c r="R54" s="14"/>
       <c r="S54" s="52"/>
     </row>
-    <row r="55" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A55" s="51"/>
       <c r="B55" s="17">
         <f t="shared" si="0"/>
@@ -6655,7 +6679,7 @@
       <c r="R55" s="20"/>
       <c r="S55" s="20"/>
     </row>
-    <row r="56" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A56" s="51"/>
       <c r="B56" s="16">
         <f>ROW(B56) - ROW($B$7)</f>
@@ -6711,7 +6735,7 @@
       <c r="R56" s="14"/>
       <c r="S56" s="52"/>
     </row>
-    <row r="57" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A57" s="51"/>
       <c r="B57" s="17">
         <f t="shared" si="0"/>
@@ -6767,7 +6791,7 @@
       <c r="R57" s="20"/>
       <c r="S57" s="20"/>
     </row>
-    <row r="58" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A58" s="51"/>
       <c r="B58" s="16">
         <f>ROW(B58) - ROW($B$7)</f>
@@ -6823,7 +6847,7 @@
       <c r="R58" s="14"/>
       <c r="S58" s="52"/>
     </row>
-    <row r="59" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A59" s="51"/>
       <c r="B59" s="17">
         <f t="shared" si="0"/>
@@ -6879,7 +6903,7 @@
       <c r="R59" s="20"/>
       <c r="S59" s="20"/>
     </row>
-    <row r="60" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A60" s="51"/>
       <c r="B60" s="16">
         <f>ROW(B60) - ROW($B$7)</f>
@@ -6935,7 +6959,7 @@
       <c r="R60" s="14"/>
       <c r="S60" s="52"/>
     </row>
-    <row r="61" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" s="53" customFormat="1">
       <c r="A61" s="51"/>
       <c r="B61" s="17">
         <f t="shared" si="0"/>
@@ -6987,7 +7011,7 @@
       <c r="R61" s="20"/>
       <c r="S61" s="20"/>
     </row>
-    <row r="62" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A62" s="51"/>
       <c r="B62" s="16">
         <f>ROW(B62) - ROW($B$7)</f>
@@ -7043,7 +7067,7 @@
       <c r="R62" s="14"/>
       <c r="S62" s="52"/>
     </row>
-    <row r="63" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A63" s="51"/>
       <c r="B63" s="17">
         <f t="shared" si="0"/>
@@ -7099,7 +7123,7 @@
       <c r="R63" s="20"/>
       <c r="S63" s="20"/>
     </row>
-    <row r="64" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A64" s="51"/>
       <c r="B64" s="16">
         <f>ROW(B64) - ROW($B$7)</f>
@@ -7155,7 +7179,7 @@
       <c r="R64" s="14"/>
       <c r="S64" s="52"/>
     </row>
-    <row r="65" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" s="53" customFormat="1">
       <c r="A65" s="51"/>
       <c r="B65" s="17">
         <f t="shared" si="0"/>
@@ -7211,7 +7235,7 @@
       <c r="R65" s="20"/>
       <c r="S65" s="20"/>
     </row>
-    <row r="66" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" s="53" customFormat="1">
       <c r="A66" s="51"/>
       <c r="B66" s="16">
         <f>ROW(B66) - ROW($B$7)</f>
@@ -7267,7 +7291,7 @@
       <c r="R66" s="14"/>
       <c r="S66" s="52"/>
     </row>
-    <row r="67" spans="1:19" s="53" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" s="53" customFormat="1" ht="48">
       <c r="A67" s="51"/>
       <c r="B67" s="17">
         <f t="shared" si="0"/>
@@ -7323,7 +7347,7 @@
       <c r="R67" s="20"/>
       <c r="S67" s="20"/>
     </row>
-    <row r="68" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A68" s="51"/>
       <c r="B68" s="16">
         <f>ROW(B68) - ROW($B$7)</f>
@@ -7379,7 +7403,7 @@
       <c r="R68" s="14"/>
       <c r="S68" s="52"/>
     </row>
-    <row r="69" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" s="53" customFormat="1">
       <c r="A69" s="51"/>
       <c r="B69" s="17">
         <f t="shared" si="0"/>
@@ -7438,7 +7462,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="70" spans="1:19" s="53" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" s="53" customFormat="1" ht="48">
       <c r="A70" s="51"/>
       <c r="B70" s="16">
         <f>ROW(B70) - ROW($B$7)</f>
@@ -7494,7 +7518,7 @@
       <c r="R70" s="14"/>
       <c r="S70" s="52"/>
     </row>
-    <row r="71" spans="1:19" s="53" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" s="53" customFormat="1" ht="48">
       <c r="A71" s="51"/>
       <c r="B71" s="17">
         <f t="shared" si="0"/>
@@ -7550,7 +7574,7 @@
       <c r="R71" s="20"/>
       <c r="S71" s="20"/>
     </row>
-    <row r="72" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" s="53" customFormat="1">
       <c r="A72" s="51"/>
       <c r="B72" s="16">
         <f>ROW(B72) - ROW($B$7)</f>
@@ -7606,7 +7630,7 @@
       <c r="R72" s="14"/>
       <c r="S72" s="52"/>
     </row>
-    <row r="73" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" s="53" customFormat="1">
       <c r="A73" s="51"/>
       <c r="B73" s="17">
         <f t="shared" si="0"/>
@@ -7662,7 +7686,7 @@
       <c r="R73" s="20"/>
       <c r="S73" s="20"/>
     </row>
-    <row r="74" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A74" s="51"/>
       <c r="B74" s="16">
         <f>ROW(B74) - ROW($B$7)</f>
@@ -7718,7 +7742,7 @@
       <c r="R74" s="14"/>
       <c r="S74" s="52"/>
     </row>
-    <row r="75" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A75" s="51"/>
       <c r="B75" s="17">
         <f t="shared" si="0"/>
@@ -7774,7 +7798,7 @@
       <c r="R75" s="20"/>
       <c r="S75" s="20"/>
     </row>
-    <row r="76" spans="1:19" s="53" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" s="53" customFormat="1" ht="25.5">
       <c r="A76" s="51"/>
       <c r="B76" s="16">
         <f>ROW(B76) - ROW($B$7)</f>
@@ -7830,7 +7854,7 @@
       <c r="R76" s="14"/>
       <c r="S76" s="52"/>
     </row>
-    <row r="77" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" s="53" customFormat="1">
       <c r="A77" s="51"/>
       <c r="B77" s="17">
         <f t="shared" si="0"/>
@@ -7886,7 +7910,7 @@
       <c r="R77" s="20"/>
       <c r="S77" s="20"/>
     </row>
-    <row r="78" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A78" s="51"/>
       <c r="B78" s="16">
         <f>ROW(B78) - ROW($B$7)</f>
@@ -7942,7 +7966,7 @@
       <c r="R78" s="14"/>
       <c r="S78" s="52"/>
     </row>
-    <row r="79" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A79" s="51"/>
       <c r="B79" s="17">
         <f t="shared" si="0"/>
@@ -7998,7 +8022,7 @@
       <c r="R79" s="20"/>
       <c r="S79" s="20"/>
     </row>
-    <row r="80" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A80" s="51"/>
       <c r="B80" s="16">
         <f>ROW(B80) - ROW($B$7)</f>
@@ -8054,7 +8078,7 @@
       <c r="R80" s="14"/>
       <c r="S80" s="52"/>
     </row>
-    <row r="81" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A81" s="51"/>
       <c r="B81" s="17">
         <f t="shared" si="0"/>
@@ -8110,7 +8134,7 @@
       <c r="R81" s="20"/>
       <c r="S81" s="20"/>
     </row>
-    <row r="82" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" s="53" customFormat="1">
       <c r="A82" s="51"/>
       <c r="B82" s="16">
         <f>ROW(B82) - ROW($B$7)</f>
@@ -8166,7 +8190,7 @@
       <c r="R82" s="14"/>
       <c r="S82" s="52"/>
     </row>
-    <row r="83" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A83" s="51"/>
       <c r="B83" s="17">
         <f t="shared" si="0"/>
@@ -8222,7 +8246,7 @@
       <c r="R83" s="20"/>
       <c r="S83" s="20"/>
     </row>
-    <row r="84" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" s="53" customFormat="1">
       <c r="A84" s="51"/>
       <c r="B84" s="16">
         <f>ROW(B84) - ROW($B$7)</f>
@@ -8278,7 +8302,7 @@
       <c r="R84" s="14"/>
       <c r="S84" s="52"/>
     </row>
-    <row r="85" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A85" s="51"/>
       <c r="B85" s="17">
         <f t="shared" si="0"/>
@@ -8334,7 +8358,7 @@
       <c r="R85" s="20"/>
       <c r="S85" s="20"/>
     </row>
-    <row r="86" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A86" s="51"/>
       <c r="B86" s="16">
         <f>ROW(B86) - ROW($B$7)</f>
@@ -8390,7 +8414,7 @@
       <c r="R86" s="14"/>
       <c r="S86" s="52"/>
     </row>
-    <row r="87" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A87" s="51"/>
       <c r="B87" s="17">
         <f t="shared" si="0"/>
@@ -8446,7 +8470,7 @@
       <c r="R87" s="20"/>
       <c r="S87" s="20"/>
     </row>
-    <row r="88" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A88" s="51"/>
       <c r="B88" s="16">
         <f>ROW(B88) - ROW($B$7)</f>
@@ -8502,7 +8526,7 @@
       <c r="R88" s="14"/>
       <c r="S88" s="52"/>
     </row>
-    <row r="89" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A89" s="51"/>
       <c r="B89" s="17">
         <f t="shared" si="0"/>
@@ -8558,7 +8582,7 @@
       <c r="R89" s="20"/>
       <c r="S89" s="20"/>
     </row>
-    <row r="90" spans="1:19" s="53" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" s="53" customFormat="1" ht="48">
       <c r="A90" s="51"/>
       <c r="B90" s="16">
         <f>ROW(B90) - ROW($B$7)</f>
@@ -8614,7 +8638,7 @@
       <c r="R90" s="14"/>
       <c r="S90" s="52"/>
     </row>
-    <row r="91" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A91" s="51"/>
       <c r="B91" s="17">
         <f t="shared" si="0"/>
@@ -8670,7 +8694,7 @@
       <c r="R91" s="20"/>
       <c r="S91" s="20"/>
     </row>
-    <row r="92" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A92" s="51"/>
       <c r="B92" s="16">
         <f>ROW(B92) - ROW($B$7)</f>
@@ -8726,7 +8750,7 @@
       <c r="R92" s="14"/>
       <c r="S92" s="52"/>
     </row>
-    <row r="93" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A93" s="51"/>
       <c r="B93" s="17">
         <f t="shared" si="0"/>
@@ -8782,7 +8806,7 @@
       <c r="R93" s="20"/>
       <c r="S93" s="20"/>
     </row>
-    <row r="94" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A94" s="51"/>
       <c r="B94" s="16">
         <f>ROW(B94) - ROW($B$7)</f>
@@ -8838,7 +8862,7 @@
       <c r="R94" s="14"/>
       <c r="S94" s="52"/>
     </row>
-    <row r="95" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" s="53" customFormat="1">
       <c r="A95" s="51"/>
       <c r="B95" s="17">
         <f t="shared" si="0"/>
@@ -8897,7 +8921,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="96" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" s="53" customFormat="1">
       <c r="A96" s="51"/>
       <c r="B96" s="16">
         <f>ROW(B96) - ROW($B$7)</f>
@@ -8953,7 +8977,7 @@
       <c r="R96" s="14"/>
       <c r="S96" s="52"/>
     </row>
-    <row r="97" spans="1:19" s="53" customFormat="1" ht="96" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" s="53" customFormat="1" ht="96">
       <c r="A97" s="51"/>
       <c r="B97" s="17">
         <f t="shared" si="0"/>
@@ -9009,7 +9033,7 @@
       <c r="R97" s="20"/>
       <c r="S97" s="20"/>
     </row>
-    <row r="98" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A98" s="51"/>
       <c r="B98" s="16">
         <f>ROW(B98) - ROW($B$7)</f>
@@ -9065,7 +9089,7 @@
       <c r="R98" s="14"/>
       <c r="S98" s="52"/>
     </row>
-    <row r="99" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" s="53" customFormat="1">
       <c r="A99" s="51"/>
       <c r="B99" s="17">
         <f t="shared" si="0"/>
@@ -9121,7 +9145,7 @@
       <c r="R99" s="20"/>
       <c r="S99" s="20"/>
     </row>
-    <row r="100" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" s="53" customFormat="1">
       <c r="A100" s="51"/>
       <c r="B100" s="16">
         <f>ROW(B100) - ROW($B$7)</f>
@@ -9177,7 +9201,7 @@
       <c r="R100" s="14"/>
       <c r="S100" s="52"/>
     </row>
-    <row r="101" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" s="53" customFormat="1">
       <c r="A101" s="51"/>
       <c r="B101" s="17">
         <f t="shared" si="0"/>
@@ -9233,7 +9257,7 @@
       <c r="R101" s="20"/>
       <c r="S101" s="20"/>
     </row>
-    <row r="102" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" s="53" customFormat="1">
       <c r="A102" s="51"/>
       <c r="B102" s="16">
         <f>ROW(B102) - ROW($B$7)</f>
@@ -9289,7 +9313,7 @@
       <c r="R102" s="14"/>
       <c r="S102" s="52"/>
     </row>
-    <row r="103" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" s="53" customFormat="1">
       <c r="A103" s="51"/>
       <c r="B103" s="17">
         <f t="shared" si="0"/>
@@ -9345,7 +9369,7 @@
       <c r="R103" s="20"/>
       <c r="S103" s="20"/>
     </row>
-    <row r="104" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" s="53" customFormat="1">
       <c r="A104" s="51"/>
       <c r="B104" s="16">
         <f>ROW(B104) - ROW($B$7)</f>
@@ -9401,7 +9425,7 @@
       <c r="R104" s="14"/>
       <c r="S104" s="52"/>
     </row>
-    <row r="105" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A105" s="51"/>
       <c r="B105" s="17">
         <f t="shared" si="0"/>
@@ -9457,7 +9481,7 @@
       <c r="R105" s="20"/>
       <c r="S105" s="20"/>
     </row>
-    <row r="106" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" s="53" customFormat="1">
       <c r="A106" s="51"/>
       <c r="B106" s="16">
         <f>ROW(B106) - ROW($B$7)</f>
@@ -9513,7 +9537,7 @@
       <c r="R106" s="14"/>
       <c r="S106" s="52"/>
     </row>
-    <row r="107" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" s="53" customFormat="1">
       <c r="A107" s="51"/>
       <c r="B107" s="17">
         <f t="shared" si="0"/>
@@ -9569,7 +9593,7 @@
       <c r="R107" s="20"/>
       <c r="S107" s="20"/>
     </row>
-    <row r="108" spans="1:19" s="53" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" s="53" customFormat="1" ht="48">
       <c r="A108" s="51"/>
       <c r="B108" s="16">
         <f>ROW(B108) - ROW($B$7)</f>
@@ -9625,7 +9649,7 @@
       <c r="R108" s="14"/>
       <c r="S108" s="52"/>
     </row>
-    <row r="109" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" s="53" customFormat="1">
       <c r="A109" s="51"/>
       <c r="B109" s="17">
         <f t="shared" si="0"/>
@@ -9681,7 +9705,7 @@
       <c r="R109" s="20"/>
       <c r="S109" s="20"/>
     </row>
-    <row r="110" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" s="53" customFormat="1">
       <c r="A110" s="51"/>
       <c r="B110" s="16">
         <f>ROW(B110) - ROW($B$7)</f>
@@ -9737,7 +9761,7 @@
       <c r="R110" s="14"/>
       <c r="S110" s="52"/>
     </row>
-    <row r="111" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A111" s="51"/>
       <c r="B111" s="17">
         <f t="shared" si="0"/>
@@ -9793,7 +9817,7 @@
       <c r="R111" s="20"/>
       <c r="S111" s="20"/>
     </row>
-    <row r="112" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" s="53" customFormat="1">
       <c r="A112" s="51"/>
       <c r="B112" s="16">
         <f>ROW(B112) - ROW($B$7)</f>
@@ -9849,7 +9873,7 @@
       <c r="R112" s="14"/>
       <c r="S112" s="52"/>
     </row>
-    <row r="113" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" s="53" customFormat="1">
       <c r="A113" s="51"/>
       <c r="B113" s="17">
         <f t="shared" si="0"/>
@@ -9905,7 +9929,7 @@
       <c r="R113" s="20"/>
       <c r="S113" s="20"/>
     </row>
-    <row r="114" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" s="53" customFormat="1">
       <c r="A114" s="51"/>
       <c r="B114" s="16">
         <f>ROW(B114) - ROW($B$7)</f>
@@ -9961,7 +9985,7 @@
       <c r="R114" s="14"/>
       <c r="S114" s="52"/>
     </row>
-    <row r="115" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" s="53" customFormat="1">
       <c r="A115" s="51"/>
       <c r="B115" s="17">
         <f t="shared" si="0"/>
@@ -10017,7 +10041,7 @@
       <c r="R115" s="20"/>
       <c r="S115" s="20"/>
     </row>
-    <row r="116" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A116" s="51"/>
       <c r="B116" s="16">
         <f>ROW(B116) - ROW($B$7)</f>
@@ -10073,7 +10097,7 @@
       <c r="R116" s="14"/>
       <c r="S116" s="52"/>
     </row>
-    <row r="117" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" s="53" customFormat="1">
       <c r="A117" s="51"/>
       <c r="B117" s="17">
         <f t="shared" si="0"/>
@@ -10129,7 +10153,7 @@
       <c r="R117" s="20"/>
       <c r="S117" s="20"/>
     </row>
-    <row r="118" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" s="53" customFormat="1">
       <c r="A118" s="51"/>
       <c r="B118" s="16">
         <f>ROW(B118) - ROW($B$7)</f>
@@ -10185,7 +10209,7 @@
       <c r="R118" s="14"/>
       <c r="S118" s="52"/>
     </row>
-    <row r="119" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" s="53" customFormat="1">
       <c r="A119" s="51"/>
       <c r="B119" s="17">
         <f t="shared" si="0"/>
@@ -10244,7 +10268,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="120" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A120" s="51"/>
       <c r="B120" s="16">
         <f>ROW(B120) - ROW($B$7)</f>
@@ -10300,7 +10324,7 @@
       <c r="R120" s="14"/>
       <c r="S120" s="52"/>
     </row>
-    <row r="121" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" s="53" customFormat="1">
       <c r="A121" s="51"/>
       <c r="B121" s="17">
         <f t="shared" si="0"/>
@@ -10356,7 +10380,7 @@
       <c r="R121" s="20"/>
       <c r="S121" s="20"/>
     </row>
-    <row r="122" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" s="53" customFormat="1">
       <c r="A122" s="51"/>
       <c r="B122" s="16">
         <f>ROW(B122) - ROW($B$7)</f>
@@ -10412,7 +10436,7 @@
       <c r="R122" s="14"/>
       <c r="S122" s="52"/>
     </row>
-    <row r="123" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" s="53" customFormat="1">
       <c r="A123" s="51"/>
       <c r="B123" s="17">
         <f t="shared" si="0"/>
@@ -10468,7 +10492,7 @@
       <c r="R123" s="20"/>
       <c r="S123" s="20"/>
     </row>
-    <row r="124" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" s="53" customFormat="1">
       <c r="A124" s="51"/>
       <c r="B124" s="16">
         <f>ROW(B124) - ROW($B$7)</f>
@@ -10524,7 +10548,7 @@
       <c r="R124" s="14"/>
       <c r="S124" s="52"/>
     </row>
-    <row r="125" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" s="53" customFormat="1">
       <c r="A125" s="51"/>
       <c r="B125" s="17">
         <f t="shared" si="0"/>
@@ -10580,7 +10604,7 @@
       <c r="R125" s="20"/>
       <c r="S125" s="20"/>
     </row>
-    <row r="126" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" s="53" customFormat="1">
       <c r="A126" s="51"/>
       <c r="B126" s="16">
         <f>ROW(B126) - ROW($B$7)</f>
@@ -10636,7 +10660,7 @@
       <c r="R126" s="14"/>
       <c r="S126" s="52"/>
     </row>
-    <row r="127" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" s="53" customFormat="1">
       <c r="A127" s="51"/>
       <c r="B127" s="17">
         <f t="shared" si="0"/>
@@ -10692,7 +10716,7 @@
       <c r="R127" s="20"/>
       <c r="S127" s="20"/>
     </row>
-    <row r="128" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" s="53" customFormat="1">
       <c r="A128" s="51"/>
       <c r="B128" s="16">
         <f>ROW(B128) - ROW($B$7)</f>
@@ -10748,7 +10772,7 @@
       <c r="R128" s="14"/>
       <c r="S128" s="52"/>
     </row>
-    <row r="129" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" s="53" customFormat="1">
       <c r="A129" s="51"/>
       <c r="B129" s="17">
         <f t="shared" si="0"/>
@@ -10807,7 +10831,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="130" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" s="53" customFormat="1">
       <c r="A130" s="51"/>
       <c r="B130" s="16">
         <f>ROW(B130) - ROW($B$7)</f>
@@ -10863,7 +10887,7 @@
       <c r="R130" s="14"/>
       <c r="S130" s="52"/>
     </row>
-    <row r="131" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" s="53" customFormat="1">
       <c r="A131" s="51"/>
       <c r="B131" s="17">
         <f t="shared" si="0"/>
@@ -10919,7 +10943,7 @@
       <c r="R131" s="20"/>
       <c r="S131" s="20"/>
     </row>
-    <row r="132" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" s="53" customFormat="1">
       <c r="A132" s="51"/>
       <c r="B132" s="16">
         <f>ROW(B132) - ROW($B$7)</f>
@@ -10975,7 +10999,7 @@
       <c r="R132" s="14"/>
       <c r="S132" s="52"/>
     </row>
-    <row r="133" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" s="53" customFormat="1">
       <c r="A133" s="51"/>
       <c r="B133" s="17">
         <f t="shared" si="0"/>
@@ -11031,7 +11055,7 @@
       <c r="R133" s="20"/>
       <c r="S133" s="20"/>
     </row>
-    <row r="134" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" s="53" customFormat="1">
       <c r="A134" s="51"/>
       <c r="B134" s="16">
         <f>ROW(B134) - ROW($B$7)</f>
@@ -11087,7 +11111,7 @@
       <c r="R134" s="14"/>
       <c r="S134" s="52"/>
     </row>
-    <row r="135" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" s="53" customFormat="1">
       <c r="A135" s="51"/>
       <c r="B135" s="17">
         <f t="shared" si="0"/>
@@ -11143,7 +11167,7 @@
       <c r="R135" s="20"/>
       <c r="S135" s="20"/>
     </row>
-    <row r="136" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" s="53" customFormat="1">
       <c r="A136" s="51"/>
       <c r="B136" s="16">
         <f>ROW(B136) - ROW($B$7)</f>
@@ -11199,7 +11223,7 @@
       <c r="R136" s="14"/>
       <c r="S136" s="52"/>
     </row>
-    <row r="137" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" s="53" customFormat="1">
       <c r="A137" s="51"/>
       <c r="B137" s="17">
         <f t="shared" si="0"/>
@@ -11255,7 +11279,7 @@
       <c r="R137" s="20"/>
       <c r="S137" s="20"/>
     </row>
-    <row r="138" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A138" s="51"/>
       <c r="B138" s="16">
         <f>ROW(B138) - ROW($B$7)</f>
@@ -11311,7 +11335,7 @@
       <c r="R138" s="14"/>
       <c r="S138" s="52"/>
     </row>
-    <row r="139" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" s="53" customFormat="1">
       <c r="A139" s="51"/>
       <c r="B139" s="17">
         <f t="shared" si="0"/>
@@ -11367,7 +11391,7 @@
       <c r="R139" s="20"/>
       <c r="S139" s="20"/>
     </row>
-    <row r="140" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" s="53" customFormat="1">
       <c r="A140" s="51"/>
       <c r="B140" s="16">
         <f>ROW(B140) - ROW($B$7)</f>
@@ -11423,7 +11447,7 @@
       <c r="R140" s="14"/>
       <c r="S140" s="52"/>
     </row>
-    <row r="141" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" s="53" customFormat="1">
       <c r="A141" s="51"/>
       <c r="B141" s="17">
         <f t="shared" si="0"/>
@@ -11479,7 +11503,7 @@
       <c r="R141" s="20"/>
       <c r="S141" s="20"/>
     </row>
-    <row r="142" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" s="53" customFormat="1">
       <c r="A142" s="51"/>
       <c r="B142" s="16">
         <f>ROW(B142) - ROW($B$7)</f>
@@ -11535,7 +11559,7 @@
       <c r="R142" s="14"/>
       <c r="S142" s="52"/>
     </row>
-    <row r="143" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" s="53" customFormat="1">
       <c r="A143" s="51"/>
       <c r="B143" s="17">
         <f t="shared" si="0"/>
@@ -11591,7 +11615,7 @@
       <c r="R143" s="20"/>
       <c r="S143" s="20"/>
     </row>
-    <row r="144" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" s="53" customFormat="1">
       <c r="A144" s="51"/>
       <c r="B144" s="16">
         <f>ROW(B144) - ROW($B$7)</f>
@@ -11647,7 +11671,7 @@
       <c r="R144" s="14"/>
       <c r="S144" s="52"/>
     </row>
-    <row r="145" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" s="53" customFormat="1">
       <c r="A145" s="51"/>
       <c r="B145" s="17">
         <f t="shared" si="0"/>
@@ -11703,7 +11727,7 @@
       <c r="R145" s="20"/>
       <c r="S145" s="20"/>
     </row>
-    <row r="146" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" s="53" customFormat="1">
       <c r="A146" s="51"/>
       <c r="B146" s="16">
         <f>ROW(B146) - ROW($B$7)</f>
@@ -11759,7 +11783,7 @@
       <c r="R146" s="14"/>
       <c r="S146" s="52"/>
     </row>
-    <row r="147" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" s="53" customFormat="1">
       <c r="A147" s="51"/>
       <c r="B147" s="17">
         <f t="shared" si="0"/>
@@ -11815,7 +11839,7 @@
       <c r="R147" s="20"/>
       <c r="S147" s="20"/>
     </row>
-    <row r="148" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" s="53" customFormat="1">
       <c r="A148" s="51"/>
       <c r="B148" s="16">
         <f>ROW(B148) - ROW($B$7)</f>
@@ -11871,7 +11895,7 @@
       <c r="R148" s="14"/>
       <c r="S148" s="52"/>
     </row>
-    <row r="149" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" s="53" customFormat="1">
       <c r="A149" s="51"/>
       <c r="B149" s="17">
         <f t="shared" si="0"/>
@@ -11927,7 +11951,7 @@
       <c r="R149" s="20"/>
       <c r="S149" s="20"/>
     </row>
-    <row r="150" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" s="53" customFormat="1">
       <c r="A150" s="51"/>
       <c r="B150" s="16">
         <f>ROW(B150) - ROW($B$7)</f>
@@ -11983,7 +12007,7 @@
       <c r="R150" s="14"/>
       <c r="S150" s="52"/>
     </row>
-    <row r="151" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" s="53" customFormat="1">
       <c r="A151" s="51"/>
       <c r="B151" s="17">
         <f t="shared" si="0"/>
@@ -12039,7 +12063,7 @@
       <c r="R151" s="20"/>
       <c r="S151" s="20"/>
     </row>
-    <row r="152" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" s="53" customFormat="1">
       <c r="A152" s="51"/>
       <c r="B152" s="16">
         <f>ROW(B152) - ROW($B$7)</f>
@@ -12095,7 +12119,7 @@
       <c r="R152" s="14"/>
       <c r="S152" s="52"/>
     </row>
-    <row r="153" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" s="53" customFormat="1">
       <c r="A153" s="51"/>
       <c r="B153" s="17">
         <f t="shared" si="0"/>
@@ -12151,7 +12175,7 @@
       <c r="R153" s="20"/>
       <c r="S153" s="20"/>
     </row>
-    <row r="154" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" s="53" customFormat="1">
       <c r="A154" s="51"/>
       <c r="B154" s="16">
         <f>ROW(B154) - ROW($B$7)</f>
@@ -12207,7 +12231,7 @@
       <c r="R154" s="14"/>
       <c r="S154" s="52"/>
     </row>
-    <row r="155" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" s="53" customFormat="1">
       <c r="A155" s="51"/>
       <c r="B155" s="17">
         <f t="shared" si="0"/>
@@ -12263,7 +12287,7 @@
       <c r="R155" s="20"/>
       <c r="S155" s="20"/>
     </row>
-    <row r="156" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" s="53" customFormat="1">
       <c r="A156" s="51"/>
       <c r="B156" s="16">
         <f>ROW(B156) - ROW($B$7)</f>
@@ -12319,7 +12343,7 @@
       <c r="R156" s="14"/>
       <c r="S156" s="52"/>
     </row>
-    <row r="157" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A157" s="51"/>
       <c r="B157" s="17">
         <f t="shared" si="0"/>
@@ -12375,7 +12399,7 @@
       <c r="R157" s="20"/>
       <c r="S157" s="20"/>
     </row>
-    <row r="158" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" s="53" customFormat="1">
       <c r="A158" s="51"/>
       <c r="B158" s="16">
         <f>ROW(B158) - ROW($B$7)</f>
@@ -12431,7 +12455,7 @@
       <c r="R158" s="14"/>
       <c r="S158" s="52"/>
     </row>
-    <row r="159" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" s="53" customFormat="1">
       <c r="A159" s="51"/>
       <c r="B159" s="17">
         <f t="shared" si="0"/>
@@ -12487,7 +12511,7 @@
       <c r="R159" s="20"/>
       <c r="S159" s="20"/>
     </row>
-    <row r="160" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" s="53" customFormat="1">
       <c r="A160" s="51"/>
       <c r="B160" s="16">
         <f>ROW(B160) - ROW($B$7)</f>
@@ -12543,7 +12567,7 @@
       <c r="R160" s="14"/>
       <c r="S160" s="52"/>
     </row>
-    <row r="161" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A161" s="51"/>
       <c r="B161" s="17">
         <f t="shared" si="0"/>
@@ -12599,7 +12623,7 @@
       <c r="R161" s="20"/>
       <c r="S161" s="20"/>
     </row>
-    <row r="162" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A162" s="51"/>
       <c r="B162" s="16">
         <f>ROW(B162) - ROW($B$7)</f>
@@ -12655,7 +12679,7 @@
       <c r="R162" s="14"/>
       <c r="S162" s="52"/>
     </row>
-    <row r="163" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A163" s="51"/>
       <c r="B163" s="17">
         <f t="shared" si="0"/>
@@ -12711,7 +12735,7 @@
       <c r="R163" s="20"/>
       <c r="S163" s="20"/>
     </row>
-    <row r="164" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" s="53" customFormat="1">
       <c r="A164" s="51"/>
       <c r="B164" s="16">
         <f>ROW(B164) - ROW($B$7)</f>
@@ -12767,7 +12791,7 @@
       <c r="R164" s="14"/>
       <c r="S164" s="52"/>
     </row>
-    <row r="165" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A165" s="51"/>
       <c r="B165" s="17">
         <f t="shared" si="0"/>
@@ -12823,7 +12847,7 @@
       <c r="R165" s="20"/>
       <c r="S165" s="20"/>
     </row>
-    <row r="166" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A166" s="51"/>
       <c r="B166" s="16">
         <f>ROW(B166) - ROW($B$7)</f>
@@ -12879,7 +12903,7 @@
       <c r="R166" s="14"/>
       <c r="S166" s="52"/>
     </row>
-    <row r="167" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" s="53" customFormat="1">
       <c r="A167" s="51"/>
       <c r="B167" s="17">
         <f t="shared" si="0"/>
@@ -12935,7 +12959,7 @@
       <c r="R167" s="20"/>
       <c r="S167" s="20"/>
     </row>
-    <row r="168" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" s="53" customFormat="1">
       <c r="A168" s="51"/>
       <c r="B168" s="16">
         <f>ROW(B168) - ROW($B$7)</f>
@@ -12991,7 +13015,7 @@
       <c r="R168" s="14"/>
       <c r="S168" s="52"/>
     </row>
-    <row r="169" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" s="53" customFormat="1">
       <c r="A169" s="51"/>
       <c r="B169" s="17">
         <f t="shared" si="0"/>
@@ -13047,7 +13071,7 @@
       <c r="R169" s="20"/>
       <c r="S169" s="20"/>
     </row>
-    <row r="170" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" s="53" customFormat="1">
       <c r="A170" s="51"/>
       <c r="B170" s="16">
         <f>ROW(B170) - ROW($B$7)</f>
@@ -13103,7 +13127,7 @@
       <c r="R170" s="14"/>
       <c r="S170" s="52"/>
     </row>
-    <row r="171" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" s="53" customFormat="1">
       <c r="A171" s="51"/>
       <c r="B171" s="17">
         <f t="shared" si="0"/>
@@ -13159,7 +13183,7 @@
       <c r="R171" s="20"/>
       <c r="S171" s="20"/>
     </row>
-    <row r="172" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A172" s="51"/>
       <c r="B172" s="16">
         <f>ROW(B172) - ROW($B$7)</f>
@@ -13215,7 +13239,7 @@
       <c r="R172" s="14"/>
       <c r="S172" s="52"/>
     </row>
-    <row r="173" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A173" s="51"/>
       <c r="B173" s="17">
         <f t="shared" si="0"/>
@@ -13271,7 +13295,7 @@
       <c r="R173" s="20"/>
       <c r="S173" s="20"/>
     </row>
-    <row r="174" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A174" s="51"/>
       <c r="B174" s="16">
         <f>ROW(B174) - ROW($B$7)</f>
@@ -13327,7 +13351,7 @@
       <c r="R174" s="14"/>
       <c r="S174" s="52"/>
     </row>
-    <row r="175" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" s="53" customFormat="1">
       <c r="A175" s="51"/>
       <c r="B175" s="17">
         <f t="shared" si="0"/>
@@ -13383,7 +13407,7 @@
       <c r="R175" s="20"/>
       <c r="S175" s="20"/>
     </row>
-    <row r="176" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A176" s="51"/>
       <c r="B176" s="16">
         <f>ROW(B176) - ROW($B$7)</f>
@@ -13439,7 +13463,7 @@
       <c r="R176" s="14"/>
       <c r="S176" s="52"/>
     </row>
-    <row r="177" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A177" s="51"/>
       <c r="B177" s="17">
         <f t="shared" si="0"/>
@@ -13495,7 +13519,7 @@
       <c r="R177" s="20"/>
       <c r="S177" s="20"/>
     </row>
-    <row r="178" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" s="53" customFormat="1">
       <c r="A178" s="51"/>
       <c r="B178" s="16">
         <f>ROW(B178) - ROW($B$7)</f>
@@ -13551,7 +13575,7 @@
       <c r="R178" s="14"/>
       <c r="S178" s="52"/>
     </row>
-    <row r="179" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" s="53" customFormat="1">
       <c r="A179" s="51"/>
       <c r="B179" s="17">
         <f t="shared" si="0"/>
@@ -13607,7 +13631,7 @@
       <c r="R179" s="20"/>
       <c r="S179" s="20"/>
     </row>
-    <row r="180" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" s="53" customFormat="1">
       <c r="A180" s="51"/>
       <c r="B180" s="16">
         <f>ROW(B180) - ROW($B$7)</f>
@@ -13663,7 +13687,7 @@
       <c r="R180" s="14"/>
       <c r="S180" s="52"/>
     </row>
-    <row r="181" spans="1:19" s="53" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" s="53" customFormat="1">
       <c r="A181" s="51"/>
       <c r="B181" s="17">
         <f t="shared" si="0"/>
@@ -13719,7 +13743,7 @@
       <c r="R181" s="20"/>
       <c r="S181" s="20"/>
     </row>
-    <row r="182" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A182" s="51"/>
       <c r="B182" s="16">
         <f>ROW(B182) - ROW($B$7)</f>
@@ -13775,7 +13799,7 @@
       <c r="R182" s="14"/>
       <c r="S182" s="52"/>
     </row>
-    <row r="183" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A183" s="51"/>
       <c r="B183" s="17">
         <f t="shared" si="0"/>
@@ -13831,7 +13855,7 @@
       <c r="R183" s="20"/>
       <c r="S183" s="20"/>
     </row>
-    <row r="184" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A184" s="51"/>
       <c r="B184" s="16">
         <f>ROW(B184) - ROW($B$7)</f>
@@ -13887,7 +13911,7 @@
       <c r="R184" s="14"/>
       <c r="S184" s="52"/>
     </row>
-    <row r="185" spans="1:19" s="53" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" s="53" customFormat="1" ht="36">
       <c r="A185" s="51"/>
       <c r="B185" s="16">
         <f t="shared" ref="B185:B187" si="171">ROW(B185) - ROW($B$7)</f>
@@ -13939,7 +13963,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="186" spans="1:19" s="53" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" s="53" customFormat="1" ht="24">
       <c r="A186" s="51"/>
       <c r="B186" s="16">
         <f t="shared" si="171"/>
@@ -13951,23 +13975,23 @@
       <c r="D186" s="14" t="s">
         <v>937</v>
       </c>
-      <c r="E186" s="14" t="s">
-        <v>938</v>
+      <c r="E186" s="62" t="s">
+        <v>939</v>
       </c>
       <c r="F186" s="14" t="s">
         <v>933</v>
       </c>
-      <c r="G186" s="14" t="s">
-        <v>939</v>
-      </c>
-      <c r="H186" s="14" t="s">
-        <v>640</v>
+      <c r="G186" s="62" t="s">
+        <v>941</v>
+      </c>
+      <c r="H186" s="62" t="s">
+        <v>943</v>
       </c>
       <c r="I186" s="14" t="s">
         <v>919</v>
       </c>
       <c r="J186" s="14" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="K186" s="14" t="s">
         <v>919</v>
@@ -13986,16 +14010,16 @@
         <v>921</v>
       </c>
       <c r="P186" s="15">
-        <v>4.5503</v>
+        <v>1.18</v>
       </c>
       <c r="Q186" s="15">
         <f t="shared" si="172"/>
-        <v>27.3018</v>
+        <v>7.08</v>
       </c>
       <c r="R186" s="14"/>
       <c r="S186" s="54"/>
     </row>
-    <row r="187" spans="1:19" s="53" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:19" s="53" customFormat="1" ht="15.75" thickBot="1">
       <c r="A187" s="51"/>
       <c r="B187" s="16">
         <f t="shared" si="171"/>
@@ -14005,53 +14029,52 @@
         <v>930</v>
       </c>
       <c r="D187" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="E187" s="62" t="s">
         <v>940</v>
-      </c>
-      <c r="E187" s="14" t="s">
-        <v>941</v>
       </c>
       <c r="F187" s="14" t="s">
         <v>933</v>
       </c>
-      <c r="G187" s="14" t="s">
+      <c r="G187" s="62" t="s">
         <v>942</v>
       </c>
-      <c r="H187" s="14" t="s">
-        <v>640</v>
+      <c r="H187" s="62" t="s">
+        <v>943</v>
       </c>
       <c r="I187" s="14" t="s">
         <v>919</v>
       </c>
       <c r="J187" s="14" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="K187" s="14" t="s">
         <v>919</v>
       </c>
       <c r="L187" s="14">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M187" s="14">
-        <f>L187*5</f>
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="N187" s="14">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="O187" s="45" t="s">
         <v>921</v>
       </c>
       <c r="P187" s="15">
-        <v>4.1700000000000001E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="Q187" s="15">
         <f t="shared" si="172"/>
-        <v>7.5060000000000002</v>
+        <v>7.4249999999999998</v>
       </c>
       <c r="R187" s="14"/>
       <c r="S187" s="54"/>
     </row>
-    <row r="188" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:19" ht="19.5" thickBot="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -14072,12 +14095,12 @@
       <c r="P188" s="58"/>
       <c r="Q188" s="18">
         <f>SUM(Q8:Q187)</f>
-        <v>642.60179999999991</v>
+        <v>622.29899999999998</v>
       </c>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
     </row>
-    <row r="189" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:19" ht="19.5" thickBot="1">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -14098,12 +14121,12 @@
       <c r="P189" s="58"/>
       <c r="Q189" s="19">
         <f>Q188/5</f>
-        <v>128.52035999999998</v>
+        <v>124.4598</v>
       </c>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
     </row>
-    <row r="201" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="13:13">
       <c r="M201" s="38"/>
     </row>
   </sheetData>
@@ -14114,180 +14137,180 @@
     <mergeCell ref="S2:S6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O8" r:id="rId1"/>
-    <hyperlink ref="O9" r:id="rId2"/>
-    <hyperlink ref="O10" r:id="rId3"/>
-    <hyperlink ref="O11" r:id="rId4"/>
-    <hyperlink ref="O12" r:id="rId5"/>
-    <hyperlink ref="O13" r:id="rId6"/>
-    <hyperlink ref="O14" r:id="rId7"/>
-    <hyperlink ref="O15" r:id="rId8"/>
-    <hyperlink ref="O16" r:id="rId9"/>
-    <hyperlink ref="O17" r:id="rId10"/>
-    <hyperlink ref="O18" r:id="rId11"/>
-    <hyperlink ref="O19" r:id="rId12"/>
-    <hyperlink ref="O20" r:id="rId13"/>
-    <hyperlink ref="O21" r:id="rId14"/>
-    <hyperlink ref="O22" r:id="rId15"/>
-    <hyperlink ref="O23" r:id="rId16"/>
-    <hyperlink ref="O24" r:id="rId17"/>
-    <hyperlink ref="O25" r:id="rId18"/>
-    <hyperlink ref="O26" r:id="rId19"/>
-    <hyperlink ref="O27" r:id="rId20"/>
-    <hyperlink ref="O28" r:id="rId21"/>
-    <hyperlink ref="O29" r:id="rId22"/>
-    <hyperlink ref="O30" r:id="rId23"/>
-    <hyperlink ref="O31" r:id="rId24"/>
-    <hyperlink ref="O32" r:id="rId25"/>
-    <hyperlink ref="O34" r:id="rId26"/>
-    <hyperlink ref="O35" r:id="rId27"/>
-    <hyperlink ref="O36" r:id="rId28"/>
-    <hyperlink ref="O37" r:id="rId29"/>
-    <hyperlink ref="O38" r:id="rId30"/>
-    <hyperlink ref="O39" r:id="rId31"/>
-    <hyperlink ref="O40" r:id="rId32"/>
-    <hyperlink ref="O41" r:id="rId33"/>
-    <hyperlink ref="O42" r:id="rId34"/>
-    <hyperlink ref="O43" r:id="rId35"/>
-    <hyperlink ref="O44" r:id="rId36"/>
-    <hyperlink ref="O45" r:id="rId37"/>
-    <hyperlink ref="O46" r:id="rId38"/>
-    <hyperlink ref="O47" r:id="rId39"/>
-    <hyperlink ref="O48" r:id="rId40"/>
-    <hyperlink ref="O49" r:id="rId41"/>
-    <hyperlink ref="O50" r:id="rId42"/>
-    <hyperlink ref="O51" r:id="rId43"/>
-    <hyperlink ref="O52" r:id="rId44"/>
-    <hyperlink ref="O53" r:id="rId45"/>
-    <hyperlink ref="O54" r:id="rId46"/>
-    <hyperlink ref="O55" r:id="rId47"/>
-    <hyperlink ref="O56" r:id="rId48"/>
-    <hyperlink ref="O57" r:id="rId49"/>
-    <hyperlink ref="O58" r:id="rId50"/>
-    <hyperlink ref="O59" r:id="rId51"/>
-    <hyperlink ref="O60" r:id="rId52"/>
-    <hyperlink ref="O61" r:id="rId53"/>
-    <hyperlink ref="O62" r:id="rId54"/>
-    <hyperlink ref="O63" r:id="rId55"/>
-    <hyperlink ref="O64" r:id="rId56"/>
-    <hyperlink ref="O65" r:id="rId57"/>
-    <hyperlink ref="O66" r:id="rId58"/>
-    <hyperlink ref="O67" r:id="rId59"/>
-    <hyperlink ref="O68" r:id="rId60"/>
-    <hyperlink ref="O70" r:id="rId61"/>
-    <hyperlink ref="O71" r:id="rId62"/>
-    <hyperlink ref="O72" r:id="rId63"/>
-    <hyperlink ref="O73" r:id="rId64"/>
-    <hyperlink ref="O74" r:id="rId65"/>
-    <hyperlink ref="O75" r:id="rId66"/>
-    <hyperlink ref="O76" r:id="rId67"/>
-    <hyperlink ref="O77" r:id="rId68"/>
-    <hyperlink ref="O78" r:id="rId69"/>
-    <hyperlink ref="O79" r:id="rId70"/>
-    <hyperlink ref="O80" r:id="rId71"/>
-    <hyperlink ref="O81" r:id="rId72"/>
-    <hyperlink ref="O82" r:id="rId73"/>
-    <hyperlink ref="O83" r:id="rId74"/>
-    <hyperlink ref="O84" r:id="rId75"/>
-    <hyperlink ref="O85" r:id="rId76"/>
-    <hyperlink ref="O86" r:id="rId77"/>
-    <hyperlink ref="O87" r:id="rId78"/>
-    <hyperlink ref="O88" r:id="rId79"/>
-    <hyperlink ref="O89" r:id="rId80"/>
-    <hyperlink ref="O90" r:id="rId81"/>
-    <hyperlink ref="O91" r:id="rId82"/>
-    <hyperlink ref="O92" r:id="rId83"/>
-    <hyperlink ref="O93" r:id="rId84"/>
-    <hyperlink ref="O94" r:id="rId85"/>
-    <hyperlink ref="O96" r:id="rId86"/>
-    <hyperlink ref="O97" r:id="rId87"/>
-    <hyperlink ref="O98" r:id="rId88"/>
-    <hyperlink ref="O99" r:id="rId89"/>
-    <hyperlink ref="O100" r:id="rId90"/>
-    <hyperlink ref="O101" r:id="rId91"/>
-    <hyperlink ref="O102" r:id="rId92"/>
-    <hyperlink ref="O103" r:id="rId93"/>
-    <hyperlink ref="O104" r:id="rId94"/>
-    <hyperlink ref="O105" r:id="rId95"/>
-    <hyperlink ref="O106" r:id="rId96"/>
-    <hyperlink ref="O107" r:id="rId97"/>
-    <hyperlink ref="O108" r:id="rId98"/>
-    <hyperlink ref="O109" r:id="rId99"/>
-    <hyperlink ref="O110" r:id="rId100"/>
-    <hyperlink ref="O111" r:id="rId101"/>
-    <hyperlink ref="O112" r:id="rId102"/>
-    <hyperlink ref="O114" r:id="rId103"/>
-    <hyperlink ref="O115" r:id="rId104"/>
-    <hyperlink ref="O116" r:id="rId105"/>
-    <hyperlink ref="O117" r:id="rId106"/>
-    <hyperlink ref="O118" r:id="rId107"/>
-    <hyperlink ref="O120" r:id="rId108"/>
-    <hyperlink ref="O121" r:id="rId109"/>
-    <hyperlink ref="O122" r:id="rId110"/>
-    <hyperlink ref="O123" r:id="rId111"/>
-    <hyperlink ref="O124" r:id="rId112"/>
-    <hyperlink ref="O125" r:id="rId113"/>
-    <hyperlink ref="O126" r:id="rId114"/>
-    <hyperlink ref="O127" r:id="rId115"/>
-    <hyperlink ref="O128" r:id="rId116"/>
-    <hyperlink ref="O130" r:id="rId117"/>
-    <hyperlink ref="O131" r:id="rId118"/>
-    <hyperlink ref="O132" r:id="rId119"/>
-    <hyperlink ref="O133" r:id="rId120"/>
-    <hyperlink ref="O134" r:id="rId121"/>
-    <hyperlink ref="O135" r:id="rId122"/>
-    <hyperlink ref="O136" r:id="rId123"/>
-    <hyperlink ref="O137" r:id="rId124"/>
-    <hyperlink ref="O138" r:id="rId125"/>
-    <hyperlink ref="O139" r:id="rId126"/>
-    <hyperlink ref="O140" r:id="rId127"/>
-    <hyperlink ref="O141" r:id="rId128"/>
-    <hyperlink ref="O142" r:id="rId129"/>
-    <hyperlink ref="O143" r:id="rId130"/>
-    <hyperlink ref="O144" r:id="rId131"/>
-    <hyperlink ref="O145" r:id="rId132"/>
-    <hyperlink ref="O146" r:id="rId133"/>
-    <hyperlink ref="O147" r:id="rId134"/>
-    <hyperlink ref="O149" r:id="rId135"/>
-    <hyperlink ref="O150" r:id="rId136"/>
-    <hyperlink ref="O151" r:id="rId137"/>
-    <hyperlink ref="O152" r:id="rId138"/>
-    <hyperlink ref="O153" r:id="rId139"/>
-    <hyperlink ref="O154" r:id="rId140"/>
-    <hyperlink ref="O155" r:id="rId141"/>
-    <hyperlink ref="O156" r:id="rId142"/>
-    <hyperlink ref="O157" r:id="rId143"/>
-    <hyperlink ref="O158" r:id="rId144"/>
-    <hyperlink ref="O159" r:id="rId145"/>
-    <hyperlink ref="O160" r:id="rId146"/>
-    <hyperlink ref="O161" r:id="rId147"/>
-    <hyperlink ref="O162" r:id="rId148"/>
-    <hyperlink ref="O163" r:id="rId149"/>
-    <hyperlink ref="O164" r:id="rId150"/>
-    <hyperlink ref="O165" r:id="rId151"/>
-    <hyperlink ref="O166" r:id="rId152"/>
-    <hyperlink ref="O167" r:id="rId153"/>
-    <hyperlink ref="O168" r:id="rId154"/>
-    <hyperlink ref="O169" r:id="rId155"/>
-    <hyperlink ref="O170" r:id="rId156"/>
-    <hyperlink ref="O171" r:id="rId157"/>
-    <hyperlink ref="O173" r:id="rId158"/>
-    <hyperlink ref="O174" r:id="rId159"/>
-    <hyperlink ref="O175" r:id="rId160"/>
-    <hyperlink ref="O177" r:id="rId161"/>
-    <hyperlink ref="O178" r:id="rId162"/>
-    <hyperlink ref="O179" r:id="rId163"/>
-    <hyperlink ref="O180" r:id="rId164"/>
-    <hyperlink ref="O181" r:id="rId165"/>
-    <hyperlink ref="O182" r:id="rId166"/>
-    <hyperlink ref="O183" r:id="rId167"/>
-    <hyperlink ref="O184" r:id="rId168"/>
-    <hyperlink ref="O176" r:id="rId169"/>
-    <hyperlink ref="O172" r:id="rId170"/>
-    <hyperlink ref="O113" r:id="rId171"/>
-    <hyperlink ref="O148" r:id="rId172"/>
-    <hyperlink ref="O186" r:id="rId173"/>
-    <hyperlink ref="O187" r:id="rId174"/>
+    <hyperlink ref="O8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="O9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="O10" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="O11" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="O12" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="O14" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="O15" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O16" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="O17" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="O18" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="O19" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O20" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="O21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="O22" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="O23" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="O24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="O25" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="O26" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="O27" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="O28" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="O29" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="O30" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="O31" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="O32" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="O34" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="O35" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="O36" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="O37" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="O38" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="O39" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="O40" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="O41" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="O42" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="O43" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="O44" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="O45" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="O46" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="O47" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="O48" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O49" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="O50" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="O51" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O52" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="O53" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="O54" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="O55" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="O56" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="O57" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="O58" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="O59" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="O60" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="O61" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="O62" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O63" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="O64" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="O65" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="O66" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="O67" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="O68" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="O70" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="O71" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="O72" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="O73" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="O74" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="O75" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="O76" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="O77" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="O78" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="O79" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="O80" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="O81" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="O82" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="O83" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="O84" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="O85" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="O86" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="O87" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="O88" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="O89" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="O90" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="O91" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="O92" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="O93" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="O94" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="O96" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="O97" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="O98" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="O99" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="O100" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="O101" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="O102" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="O103" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="O104" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="O105" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="O106" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="O107" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="O108" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="O109" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="O110" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="O111" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="O112" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="O114" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="O115" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="O116" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="O117" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="O118" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="O120" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="O121" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="O122" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="O123" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="O124" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="O125" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="O126" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="O127" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="O128" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="O130" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="O131" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="O132" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="O133" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="O134" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="O135" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="O136" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="O137" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="O138" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="O139" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="O140" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="O141" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="O142" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="O143" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="O144" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="O145" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="O146" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="O147" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="O149" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="O150" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="O151" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="O152" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="O153" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="O154" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="O155" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="O156" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="O157" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="O158" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="O159" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="O160" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="O161" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="O162" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="O163" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="O164" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="O165" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="O166" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="O167" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="O168" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="O169" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="O170" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="O171" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="O173" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="O174" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="O175" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="O177" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="O178" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="O179" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="O180" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="O181" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="O182" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="O183" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="O184" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="O176" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="O172" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="O113" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="O148" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="O186" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="O187" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId175"/>
